--- a/forms/dist/obs_camp_registration.xlsx
+++ b/forms/dist/obs_camp_registration.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="entities" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -460,6 +461,8 @@
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,6 +539,16 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>parameters</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>choice_filter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>save_to</t>
         </is>
       </c>
     </row>
@@ -563,6 +576,8 @@
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -588,6 +603,8 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -613,6 +630,8 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -638,6 +657,8 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -663,6 +684,8 @@
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -700,6 +723,8 @@
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -733,6 +758,8 @@
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -774,6 +801,8 @@
       </c>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -815,6 +844,8 @@
       </c>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -840,6 +871,8 @@
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -869,6 +902,8 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -898,105 +933,99 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>csv-external</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>persons</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>consent</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>സമ്മതം</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>consent_care</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>[Replace with ethics-approved text] Check-ups and medicines at this camp are free for everyone.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>[അംഗീകരിച്ച സമ്മതപത്രം ഇവിടെ ചേർക്കുക] ഈ ക്യാമ്പിലെ പരിശോധനയും മരുന്നും എല്ലാവർക്കും സൗജന്യമാണ്.</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>consent_research</t>
+          <t>consent_care</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>May we use this information, without names, for the water and health study? Care is the same whether or not you agree.</t>
+          <t>[Replace with ethics-approved text] Check-ups and medicines at this camp are free for everyone.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>പേര് ഒഴിവാക്കി ഈ വിവരങ്ങൾ ജല-ആരോഗ്യ പഠനത്തിനായി ഉപയോഗിക്കാൻ സമ്മതമാണോ? സമ്മതിച്ചാലും ഇല്ലെങ്കിലും ചികിത്സ ഒരുപോലെ ലഭിക്കും.</t>
+          <t>[അംഗീകരിച്ച സമ്മതപത്രം ഇവിടെ ചേർക്കുക] ഈ ക്യാമ്പിലെ പരിശോധനയും മരുന്നും എല്ലാവർക്കും സൗജന്യമാണ്.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1005,53 +1034,61 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>consent</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>select_one yes_no</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>consent_research</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>May we use this information, without names, for the water and health study? Care is the same whether or not you agree.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>പേര് ഒഴിവാക്കി ഈ വിവരങ്ങൾ ജല-ആരോഗ്യ പഠനത്തിനായി ഉപയോഗിക്കാൻ സമ്മതമാണോ? സമ്മതിച്ചാലും ഇല്ലെങ്കിലും ചികിത്സ ഒരുപോലെ ലഭിക്കും.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>pid</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>വ്യക്തിയുടെ ഐഡി</t>
-        </is>
-      </c>
+          <t>consent</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr"/>
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr"/>
@@ -1061,73 +1098,69 @@
       <c r="K18" s="3" t="inlineStr"/>
       <c r="L18" s="3" t="inlineStr"/>
       <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>pid</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Person ID</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>വ്യക്തിയുടെ ഐഡി</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>select_one id_method</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>pid_method</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Person ID: scan or type?</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>വ്യക്തിയുടെ ഐഡി: സ്കാൻ ചെയ്യണോ ടൈപ്പ് ചെയ്യണോ?</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>scan</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>barcode</t>
+          <t>select_one id_method</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>pid_scan</t>
+          <t>pid_method</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Scan the person ID sticker on the health card</t>
+          <t>Person ID: scan or type?</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ഹെൽത്ത് കാർഡിലെ ഐഡി സ്റ്റിക്കർ സ്കാൻ ചെയ്യുക</t>
+          <t>വ്യക്തിയുടെ ഐഡി: സ്കാൻ ചെയ്യണോ ടൈപ്പ് ചെയ്യണോ?</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1137,62 +1170,44 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>${pid_method}='scan'</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>regex(., '^OBS-P-[0-9]{6}$')</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>This is not a person ID sticker (format OBS-P-000123).</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>ഇത് വ്യക്തിയുടെ ഐഡി സ്റ്റിക്കർ അല്ല (ഉദാ: OBS-P-000123).</t>
-        </is>
-      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>barcode</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>pid_type</t>
+          <t>pid_scan</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Type the person ID</t>
+          <t>Scan the person ID sticker on the health card</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>വ്യക്തിയുടെ ഐഡി ടൈപ്പ് ചെയ്യുക</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Format: OBS-P-000123</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>ഉദാ: OBS-P-000123</t>
-        </is>
-      </c>
+          <t>ഹെൽത്ത് കാർഡിലെ ഐഡി സ്റ്റിക്കർ സ്കാൻ ചെയ്യുക</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1200,7 +1215,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>${pid_method}='type'</t>
+          <t>${pid_method}='scan'</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1210,170 +1225,204 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Use the format OBS-P-000123.</t>
+          <t>This is not a person ID sticker (format OBS-P-000123).</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>OBS-P-000123 എന്ന രൂപത്തിൽ നൽകുക.</t>
+          <t>ഇത് വ്യക്തിയുടെ ഐഡി സ്റ്റിക്കർ അല്ല (ഉദാ: OBS-P-000123).</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>pid_type</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Type the person ID</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>വ്യക്തിയുടെ ഐഡി ടൈപ്പ് ചെയ്യുക</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Format: OBS-P-000123</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>ഉദാ: OBS-P-000123</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>${pid_method}='type'</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>regex(., '^OBS-P-[0-9]{6}$')</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Use the format OBS-P-000123.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>OBS-P-000123 എന്ന രൂപത്തിൽ നൽകുക.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>pid</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
-      <c r="O22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>person_id</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>if(${pid_method}='scan', ${pid_scan}, ${pid_type})</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>person_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>hid</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Household ID</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>വീടിന്റെ ഐഡി</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="3" t="inlineStr"/>
-      <c r="N24" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>select_one id_method</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>hh_method</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Household ID: scan or type?</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>വീടിന്റെ ഐഡി: സ്കാൻ ചെയ്യണോ ടൈപ്പ് ചെയ്യണോ?</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>scan</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>barcode</t>
+          <t>select_one id_method</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>hh_scan</t>
+          <t>hh_method</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Scan the household sticker</t>
+          <t>Household ID: scan or type?</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>വീടിന്റെ സ്റ്റിക്കർ സ്കാൻ ചെയ്യുക</t>
+          <t>വീടിന്റെ ഐഡി: സ്കാൻ ചെയ്യണോ ടൈപ്പ് ചെയ്യണോ?</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1383,62 +1432,44 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>${hh_method}='scan'</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>regex(., '^[A-Z]{2,4}-[0-9]{3}$')</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>This is not a household sticker (format CVB-014).</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>ഇത് വീടിന്റെ സ്റ്റിക്കർ അല്ല (ഉദാ: CVB-014).</t>
-        </is>
-      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>barcode</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>hh_type</t>
+          <t>hh_scan</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Type the household ID</t>
+          <t>Scan the household sticker</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>വീടിന്റെ ഐഡി ടൈപ്പ് ചെയ്യുക</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Format: CVB-014</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>ഉദാ: CVB-014</t>
-        </is>
-      </c>
+          <t>വീടിന്റെ സ്റ്റിക്കർ സ്കാൻ ചെയ്യുക</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1446,7 +1477,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>${hh_method}='type'</t>
+          <t>${hh_method}='scan'</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1456,223 +1487,255 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Use the format CVB-014.</t>
+          <t>This is not a household sticker (format CVB-014).</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>CVB-014 എന്ന രൂപത്തിൽ നൽകുക.</t>
+          <t>ഇത് വീടിന്റെ സ്റ്റിക്കർ അല്ല (ഉദാ: CVB-014).</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>hh_type</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Type the household ID</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>വീടിന്റെ ഐഡി ടൈപ്പ് ചെയ്യുക</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Format: CVB-014</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>ഉദാ: CVB-014</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>${hh_method}='type'</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>regex(., '^[A-Z]{2,4}-[0-9]{3}$')</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Use the format CVB-014.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>CVB-014 എന്ന രൂപത്തിൽ നൽകുക.</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>hid</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr"/>
-      <c r="N28" s="3" t="inlineStr"/>
-      <c r="O28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>hh_id</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>if(${hh_method}='scan', ${hh_scan}, ${hh_type})</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>hh_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>About the person</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>വ്യക്തിയെ കുറിച്ച്</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr"/>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr"/>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>പേര്</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Manglish or Malayalam keyboard both work.</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>മംഗ്ലീഷ് അല്ലെങ്കിൽ മലയാളം കീബോർഡ് ഉപയോഗിക്കാം.</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Age (years)</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>പ്രായം (വർഷം)</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
+          <t>പേര്</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Manglish or Malayalam keyboard both work.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>മംഗ്ലീഷ് അല്ലെങ്കിൽ മലയാളം കീബോർഡ് ഉപയോഗിക്കാം.</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 120</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Please check this value.</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>ഈ മൂല്യം ഒന്നുകൂടി പരിശോധിക്കുക.</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>select_one sex</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Age (years)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ലിംഗം</t>
+          <t>പ്രായം (വർഷം)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1683,222 +1746,246 @@
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 120</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Please check this value.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>ഈ മൂല്യം ഒന്നുകൂടി പരിശോധിക്കുക.</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>horizontal-compact</t>
-        </is>
-      </c>
+      <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sex</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Phone number (for results)</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ഫോൺ നമ്പർ (ഫലം അറിയിക്കാൻ)</t>
+          <t>ലിംഗം</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>regex(., '^[6-9][0-9]{9}$')</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Enter a 10-digit mobile number.</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>10 അക്ക മൊബൈൽ നമ്പർ നൽകുക.</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>numbers</t>
+          <t>horizontal-compact</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>resident</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Does this person live here permanently?</t>
+          <t>Phone number (for results)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ഈ വ്യക്തി ഇവിടെ സ്ഥിരതാമസമാണോ?</t>
+          <t>ഫോൺ നമ്പർ (ഫലം അറിയിക്കാൻ)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>regex(., '^[6-9][0-9]{9}$')</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Enter a 10-digit mobile number.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>10 അക്ക മൊബൈൽ നമ്പർ നൽകുക.</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>numbers</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>select_one yes_no</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Does this person live here permanently?</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>ഈ വ്യക്തി ഇവിടെ സ്ഥിരതാമസമാണോ?</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>horizontal-compact</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
-      <c r="O36" s="3" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Visitor details</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>സന്ദർശകന്റെ വിവരങ്ങൾ</t>
-        </is>
-      </c>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>${resident}='no'</t>
-        </is>
-      </c>
+      <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="inlineStr"/>
       <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr">
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Visitor details</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>സന്ദർശകന്റെ വിവരങ്ങൾ</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>${resident}='no'</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>home_address</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Home address</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>വീട്ടു വിലാസം</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Tip: tap the microphone key on the keyboard and speak, in Malayalam or English.</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>കീബോർഡിലെ മൈക്ക് അമർത്തി മലയാളത്തിലോ ഇംഗ്ലീഷിലോ പറഞ്ഞാൽ മതി.</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1908,22 +1995,34 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>home_lsg</t>
+          <t>home_address</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Panchayat / municipality / ward</t>
+          <t>Home address</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>പഞ്ചായത്ത് / നഗരസഭ / വാർഡ്</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t>വീട്ടു വിലാസം</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Tip: tap the microphone key on the keyboard and speak, in Malayalam or English.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>കീബോർഡിലെ മൈക്ക് അമർത്തി മലയാളത്തിലോ ഇംഗ്ലീഷിലോ പറഞ്ഞാൽ മതി.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
@@ -1932,26 +2031,28 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>select_one stay</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>stay</t>
+          <t>home_lsg</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>How long staying here?</t>
+          <t>Panchayat / municipality / ward</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>ഇവിടെ എത്ര കാലമായി താമസിക്കുന്നു?</t>
+          <t>പഞ്ചായത്ത് / നഗരസഭ / വാർഡ്</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -1965,113 +2066,117 @@
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>select_one stay</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>stay</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>How long staying here?</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>ഇവിടെ എത്ര കാലമായി താമസിക്കുന്നു?</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
-      <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
-      <c r="O41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>first_member</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Is this the first person from this household registered at this camp?</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>ഈ ക്യാമ്പിൽ ഈ വീട്ടിൽ നിന്ന് ആദ്യം രജിസ്റ്റർ ചെയ്യുന്നത് ഇദ്ദേഹമാണോ?</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>${consent_research}='yes' and ${resident}='yes'</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>horizontal-compact</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>household</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Part A: Household and water</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>ഭാഗം A: വീടും വെള്ളവും</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>${consent_research}='yes' and ${resident}='yes' and ${first_member}='yes'</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2081,83 +2186,75 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>hh_people</t>
+          <t>household</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>People in the house</t>
+          <t>Part A: Household and water</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>വീട്ടിലെ ആളുകൾ</t>
+          <t>ഭാഗം A: വീടും വെള്ളവും</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>${consent_research}='yes' and ${resident}='yes' and ${first_member}='yes'</t>
+        </is>
+      </c>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="3" t="inlineStr"/>
       <c r="L44" s="3" t="inlineStr"/>
       <c r="M44" s="3" t="inlineStr"/>
-      <c r="N44" s="3" t="inlineStr">
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>hh_people</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>People in the house</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>വീട്ടിലെ ആളുകൾ</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>hh_size</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Number of people living in this house</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>ഈ വീട്ടിൽ താമസിക്കുന്നവരുടെ എണ്ണം</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 30</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Please check this value.</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>ഈ മൂല്യം ഒന്നുകൂടി പരിശോധിക്കുക.</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2167,17 +2264,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>hh_n60</t>
+          <t>hh_size</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>How many are aged 60 or above?</t>
+          <t>Number of people living in this house</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>ഇതിൽ 60 വയസ്സോ അതിനു മുകളിലോ ഉള്ളവർ എത്ര?</t>
+          <t>ഈ വീട്ടിൽ താമസിക്കുന്നവരുടെ എണ്ണം</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2190,7 +2287,7 @@
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= ${hh_size}</t>
+          <t>. &gt;= 1 and . &lt;= 30</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -2207,6 +2304,8 @@
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2216,17 +2315,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>hh_n5</t>
+          <t>hh_n60</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>How many children under 5?</t>
+          <t>How many are aged 60 or above?</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>5 വയസ്സിൽ താഴെയുള്ള കുട്ടികൾ എത്ര?</t>
+          <t>ഇതിൽ 60 വയസ്സോ അതിനു മുകളിലോ ഉള്ളവർ എത്ര?</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2256,53 +2355,73 @@
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>hh_people</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr"/>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr"/>
-      <c r="K48" s="3" t="inlineStr"/>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="3" t="inlineStr"/>
-      <c r="N48" s="3" t="inlineStr"/>
-      <c r="O48" s="3" t="inlineStr"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>hh_n5</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>How many children under 5?</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>5 വയസ്സിൽ താഴെയുള്ള കുട്ടികൾ എത്ര?</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${hh_size}</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Please check this value.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>ഈ മൂല്യം ഒന്നുകൂടി പരിശോധിക്കുക.</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>hh_water</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Drinking water</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>കുടിവെള്ളം</t>
-        </is>
-      </c>
+          <t>hh_people</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr"/>
@@ -2312,69 +2431,69 @@
       <c r="K49" s="3" t="inlineStr"/>
       <c r="L49" s="3" t="inlineStr"/>
       <c r="M49" s="3" t="inlineStr"/>
-      <c r="N49" s="3" t="inlineStr">
+      <c r="N49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>hh_water</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Drinking water</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>കുടിവെള്ളം</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>select_one water_src</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>water_drink</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Main source of drinking water</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>കുടിവെള്ളത്തിന്റെ പ്രധാന ഉറവിടം</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one water_src</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>cook_same</t>
+          <t>water_drink</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Same water used for cooking?</t>
+          <t>Main source of drinking water</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>പാചകത്തിനും ഇതേ വെള്ളമാണോ?</t>
+          <t>കുടിവെള്ളത്തിന്റെ പ്രധാന ഉറവിടം</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2390,32 +2509,30 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>horizontal-compact</t>
-        </is>
-      </c>
+      <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>select_one water_src</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>water_cook</t>
+          <t>cook_same</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Water for cooking</t>
+          <t>Same water used for cooking?</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>പാചകത്തിനുള്ള വെള്ളം</t>
+          <t>പാചകത്തിനും ഇതേ വെള്ളമാണോ?</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2425,38 +2542,40 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>${cook_same}='no'</t>
-        </is>
-      </c>
+      <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>horizontal-compact</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>select_multiple treat</t>
+          <t>select_one water_src</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>treat</t>
+          <t>water_cook</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>How is drinking water treated?</t>
+          <t>Water for cooking</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>കുടിവെള്ളം എങ്ങനെ ശുദ്ധീകരിക്കുന്നു?</t>
+          <t>പാചകത്തിനുള്ള വെള്ളം</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2466,46 +2585,40 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>not(selected(., 'none') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>'None' cannot be combined with other answers.</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>'ഒന്നുമില്ല' മറ്റ് ഉത്തരങ്ങളോടൊപ്പം തിരഞ്ഞെടുക്കാൻ പാടില്ല.</t>
-        </is>
-      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>${cook_same}='no'</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>select_one storage</t>
+          <t>select_multiple treat</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>storage</t>
+          <t>treat</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>How is drinking water stored?</t>
+          <t>How is drinking water treated?</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>കുടിവെള്ളം എങ്ങനെ സൂക്ഷിക്കുന്നു?</t>
+          <t>കുടിവെള്ളം എങ്ങനെ ശുദ്ധീകരിക്കുന്നു?</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -2516,60 +2629,80 @@
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>not(selected(., 'none') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>'None' cannot be combined with other answers.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>'ഒന്നുമില്ല' മറ്റ് ഉത്തരങ്ങളോടൊപ്പം തിരഞ്ഞെടുക്കാൻ പാടില്ല.</t>
+        </is>
+      </c>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>hh_water</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr"/>
-      <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr"/>
-      <c r="M55" s="3" t="inlineStr"/>
-      <c r="N55" s="3" t="inlineStr"/>
-      <c r="O55" s="3" t="inlineStr"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>select_one storage</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>How is drinking water stored?</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>കുടിവെള്ളം എങ്ങനെ സൂക്ഷിക്കുന്നു?</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>hh_salt</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Salt and sanitation</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>ഉപ്പുരസവും ശുചിത്വവും</t>
-        </is>
-      </c>
+          <t>hh_water</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr"/>
+      <c r="D56" s="3" t="inlineStr"/>
       <c r="E56" s="3" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="3" t="inlineStr"/>
@@ -2579,79 +2712,79 @@
       <c r="K56" s="3" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr"/>
       <c r="M56" s="3" t="inlineStr"/>
-      <c r="N56" s="3" t="inlineStr">
+      <c r="N56" s="3" t="inlineStr"/>
+      <c r="O56" s="3" t="inlineStr"/>
+      <c r="P56" s="3" t="inlineStr"/>
+      <c r="Q56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>hh_salt</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Salt and sanitation</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>ഉപ്പുരസവും ശുചിത്വവും</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>select_one freq3</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>salty</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Does your well or tap water ever taste salty?</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>കിണർ / പൈപ്പ് വെള്ളത്തിന് ഉപ്പുരസം തോന്നാറുണ്ടോ?</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
-      <c r="O57" s="2" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>select_multiple season</t>
+          <t>select_one freq3</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>salty_season</t>
+          <t>salty</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>In which season?</t>
+          <t>Does your well or tap water ever taste salty?</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>ഏത് കാലത്ത്?</t>
+          <t>കിണർ / പൈപ്പ് വെള്ളത്തിന് ഉപ്പുരസം തോന്നാറുണ്ടോ?</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>${salty}!='never'</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
@@ -2659,36 +2792,38 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>select_one toilet</t>
+          <t>select_multiple season</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>salty_season</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Type of toilet</t>
+          <t>In which season?</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>ശൗചാലയത്തിന്റെ തരം</t>
+          <t>ഏത് കാലത്ത്?</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>${salty}!='never'</t>
+        </is>
+      </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
@@ -2696,36 +2831,38 @@
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>select_one dist</t>
+          <t>select_one toilet</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>septic_dist</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Distance from septic tank or pit to the well</t>
+          <t>Type of toilet</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>സെപ്റ്റിക് ടാങ്കിൽ / കുഴിയിൽ നിന്ന് കിണറിലേക്കുള്ള ദൂരം</t>
+          <t>ശൗചാലയത്തിന്റെ തരം</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>selected(${water_drink}, 'own_well') or selected(${water_drink}, 'shared_well')</t>
-        </is>
-      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
@@ -2733,53 +2870,61 @@
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>hh_salt</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="3" t="inlineStr"/>
-      <c r="J61" s="3" t="inlineStr"/>
-      <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="3" t="inlineStr"/>
-      <c r="N61" s="3" t="inlineStr"/>
-      <c r="O61" s="3" t="inlineStr"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>select_one dist</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>septic_dist</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Distance from septic tank or pit to the well</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>സെപ്റ്റിക് ടാങ്കിൽ / കുഴിയിൽ നിന്ന് കിണറിലേക്കുള്ള ദൂരം</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>selected(${water_drink}, 'own_well') or selected(${water_drink}, 'shared_well')</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>hh_flood</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Flooding and animals</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>വെള്ളപ്പൊക്കവും മൃഗങ്ങളും</t>
-        </is>
-      </c>
+          <t>hh_salt</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr"/>
       <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" s="3" t="inlineStr"/>
@@ -2789,73 +2934,69 @@
       <c r="K62" s="3" t="inlineStr"/>
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
-      <c r="N62" s="3" t="inlineStr">
+      <c r="N62" s="3" t="inlineStr"/>
+      <c r="O62" s="3" t="inlineStr"/>
+      <c r="P62" s="3" t="inlineStr"/>
+      <c r="Q62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>hh_flood</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Flooding and animals</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>വെള്ളപ്പൊക്കവും മൃഗങ്ങളും</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
+      <c r="N63" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>select_one yes_no</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>flood</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>In the past 12 months, did water enter the house or compound?</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>കഴിഞ്ഞ 12 മാസത്തിൽ വെള്ളം വീട്ടിലോ മുറ്റത്തോ കയറിയോ?</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>horizontal-compact</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr"/>
+      <c r="O63" s="3" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr"/>
+      <c r="Q63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>flood_times</t>
+          <t>flood</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>How many times?</t>
+          <t>In the past 12 months, did water enter the house or compound?</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>എത്ര തവണ?</t>
+          <t>കഴിഞ്ഞ 12 മാസത്തിൽ വെള്ളം വീട്ടിലോ മുറ്റത്തോ കയറിയോ?</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -2865,50 +3006,40 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>${flood}='yes'</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 50</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>Please check this value.</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>ഈ മൂല്യം ഒന്നുകൂടി പരിശോധിക്കുക.</t>
-        </is>
-      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>horizontal-compact</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>select_multiple animals</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>animals</t>
+          <t>flood_times</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Animals or birds kept at home</t>
+          <t>How many times?</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>വീട്ടിൽ വളർത്തുന്ന മൃഗങ്ങൾ / പക്ഷികൾ</t>
+          <t>എത്ര തവണ?</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -2918,46 +3049,52 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>${flood}='yes'</t>
+        </is>
+      </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>not(selected(., 'none') and count-selected(.) &gt; 1)</t>
+          <t>. &gt;= 1 and . &lt;= 50</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>'None' cannot be combined with other answers.</t>
+          <t>Please check this value.</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>'ഒന്നുമില്ല' മറ്റ് ഉത്തരങ്ങളോടൊപ്പം തിരഞ്ഞെടുക്കാൻ പാടില്ല.</t>
+          <t>ഈ മൂല്യം ഒന്നുകൂടി പരിശോധിക്കുക.</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>select_one freq3</t>
+          <t>select_multiple animals</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>rats</t>
+          <t>animals</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Do you see rats around the house or water storage?</t>
+          <t>Animals or birds kept at home</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>വീടിനു ചുറ്റും / വെള്ളം സൂക്ഷിക്കുന്നിടത്ത് എലികളെ കാണാറുണ്ടോ?</t>
+          <t>വീട്ടിൽ വളർത്തുന്ന മൃഗങ്ങൾ / പക്ഷികൾ</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -2968,132 +3105,156 @@
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>not(selected(., 'none') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>'None' cannot be combined with other answers.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>'ഒന്നുമില്ല' മറ്റ് ഉത്തരങ്ങളോടൊപ്പം തിരഞ്ഞെടുക്കാൻ പാടില്ല.</t>
+        </is>
+      </c>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>hh_flood</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="3" t="inlineStr"/>
-      <c r="K67" s="3" t="inlineStr"/>
-      <c r="L67" s="3" t="inlineStr"/>
-      <c r="M67" s="3" t="inlineStr"/>
-      <c r="N67" s="3" t="inlineStr"/>
-      <c r="O67" s="3" t="inlineStr"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>select_one freq3</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>rats</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Do you see rats around the house or water storage?</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>വീടിനു ചുറ്റും / വെള്ളം സൂക്ഷിക്കുന്നിടത്ത് എലികളെ കാണാറുണ്ടോ?</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>hh_flats</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Flats: sump and tank</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>ഫ്ലാറ്റ്: സംപും ടാങ്കും</t>
-        </is>
-      </c>
+          <t>hh_flood</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr"/>
       <c r="E68" s="3" t="inlineStr"/>
       <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>${site_type}='flats'</t>
-        </is>
-      </c>
+      <c r="H68" s="3" t="inlineStr"/>
       <c r="I68" s="3" t="inlineStr"/>
       <c r="J68" s="3" t="inlineStr"/>
       <c r="K68" s="3" t="inlineStr"/>
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
-      <c r="N68" s="3" t="inlineStr">
+      <c r="N68" s="3" t="inlineStr"/>
+      <c r="O68" s="3" t="inlineStr"/>
+      <c r="P68" s="3" t="inlineStr"/>
+      <c r="Q68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>hh_flats</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Flats: sump and tank</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>ഫ്ലാറ്റ്: സംപും ടാങ്കും</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>${site_type}='flats'</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr"/>
+      <c r="L69" s="3" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr"/>
+      <c r="N69" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>select_one sump_mgr</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>sump_mgr</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Who manages the sump and tank?</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>സംപും ടാങ്കും ആരാണ് നോക്കുന്നത്?</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr"/>
-      <c r="O69" s="2" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr"/>
+      <c r="P69" s="3" t="inlineStr"/>
+      <c r="Q69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>select_one last_clean</t>
+          <t>select_one sump_mgr</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>tank_clean</t>
+          <t>sump_mgr</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>When was the tank last cleaned?</t>
+          <t>Who manages the sump and tank?</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>ടാങ്ക് അവസാനമായി വൃത്തിയാക്കിയത് എപ്പോൾ?</t>
+          <t>സംപും ടാങ്കും ആരാണ് നോക്കുന്നത്?</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -3107,53 +3268,57 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>hh_flats</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr"/>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
-      <c r="K71" s="3" t="inlineStr"/>
-      <c r="L71" s="3" t="inlineStr"/>
-      <c r="M71" s="3" t="inlineStr"/>
-      <c r="N71" s="3" t="inlineStr"/>
-      <c r="O71" s="3" t="inlineStr"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>select_one last_clean</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>tank_clean</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>When was the tank last cleaned?</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>ടാങ്ക് അവസാനമായി വൃത്തിയാക്കിയത് എപ്പോൾ?</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>hh_tds</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>Water salt test (TDS)</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>വെള്ളത്തിലെ ഉപ്പ് പരിശോധന (TDS)</t>
-        </is>
-      </c>
+          <t>hh_flats</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr"/>
       <c r="E72" s="3" t="inlineStr"/>
       <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr"/>
@@ -3163,73 +3328,69 @@
       <c r="K72" s="3" t="inlineStr"/>
       <c r="L72" s="3" t="inlineStr"/>
       <c r="M72" s="3" t="inlineStr"/>
-      <c r="N72" s="3" t="inlineStr">
+      <c r="N72" s="3" t="inlineStr"/>
+      <c r="O72" s="3" t="inlineStr"/>
+      <c r="P72" s="3" t="inlineStr"/>
+      <c r="Q72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>hh_tds</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Water salt test (TDS)</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>വെള്ളത്തിലെ ഉപ്പ് പരിശോധന (TDS)</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr"/>
+      <c r="F73" s="3" t="inlineStr"/>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="3" t="inlineStr"/>
+      <c r="L73" s="3" t="inlineStr"/>
+      <c r="M73" s="3" t="inlineStr"/>
+      <c r="N73" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>select_one yes_no</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>bottle</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Did they bring a bottle of their drinking water?</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>കുടിവെള്ളം കുപ്പിയിൽ കൊണ്ടുവന്നിട്ടുണ്ടോ?</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>horizontal-compact</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr"/>
+      <c r="O73" s="3" t="inlineStr"/>
+      <c r="P73" s="3" t="inlineStr"/>
+      <c r="Q73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>tds</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>TDS meter reading (mg/L)</t>
+          <t>Did they bring a bottle of their drinking water?</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>TDS മീറ്റർ റീഡിംഗ് (mg/L)</t>
+          <t>കുടിവെള്ളം കുപ്പിയിൽ കൊണ്ടുവന്നിട്ടുണ്ടോ?</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -3239,92 +3400,114 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>${bottle}='yes'</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 20000</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>Please check this value.</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>ഈ മൂല്യം ഒന്നുകൂടി പരിശോധിക്കുക.</t>
-        </is>
-      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>horizontal-compact</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>tds_flag</t>
+          <t>tds</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Reading above 1,000 mg/L: tell the person their water tastes salty for a reason, and mark the health card.</t>
+          <t>TDS meter reading (mg/L)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>1000 mg/L-ൽ കൂടുതൽ: വെള്ളത്തിൽ ഉപ്പ് കൂടുതലാണെന്ന് പറയുക, ഹെൽത്ത് കാർഡിൽ രേഖപ്പെടുത്തുക.</t>
+          <t>TDS മീറ്റർ റീഡിംഗ് (mg/L)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>${tds} &gt; 1000</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr"/>
+          <t>${bottle}='yes'</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 20000</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Please check this value.</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>ഈ മൂല്യം ഒന്നുകൂടി പരിശോധിക്കുക.</t>
+        </is>
+      </c>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>hh_tds</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr"/>
-      <c r="D76" s="3" t="inlineStr"/>
-      <c r="E76" s="3" t="inlineStr"/>
-      <c r="F76" s="3" t="inlineStr"/>
-      <c r="G76" s="3" t="inlineStr"/>
-      <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="3" t="inlineStr"/>
-      <c r="K76" s="3" t="inlineStr"/>
-      <c r="L76" s="3" t="inlineStr"/>
-      <c r="M76" s="3" t="inlineStr"/>
-      <c r="N76" s="3" t="inlineStr"/>
-      <c r="O76" s="3" t="inlineStr"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>tds_flag</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Reading above 1,000 mg/L: tell the person their water tastes salty for a reason, and mark the health card.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>1000 mg/L-ൽ കൂടുതൽ: വെള്ളത്തിൽ ഉപ്പ് കൂടുതലാണെന്ന് പറയുക, ഹെൽത്ത് കാർഡിൽ രേഖപ്പെടുത്തുക.</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>${tds} &gt; 1000</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -3334,7 +3517,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>household</t>
+          <t>hh_tds</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr"/>
@@ -3350,36 +3533,26 @@
       <c r="M77" s="3" t="inlineStr"/>
       <c r="N77" s="3" t="inlineStr"/>
       <c r="O77" s="3" t="inlineStr"/>
+      <c r="P77" s="3" t="inlineStr"/>
+      <c r="Q77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>indiv</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>Part B: Recent illness</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>ഭാഗം B: അടുത്തിടെയുള്ള അസുഖങ്ങൾ</t>
-        </is>
-      </c>
+          <t>household</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr"/>
+      <c r="D78" s="3" t="inlineStr"/>
       <c r="E78" s="3" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>${consent_research}='yes'</t>
-        </is>
-      </c>
+      <c r="H78" s="3" t="inlineStr"/>
       <c r="I78" s="3" t="inlineStr"/>
       <c r="J78" s="3" t="inlineStr"/>
       <c r="K78" s="3" t="inlineStr"/>
@@ -3387,6 +3560,8 @@
       <c r="M78" s="3" t="inlineStr"/>
       <c r="N78" s="3" t="inlineStr"/>
       <c r="O78" s="3" t="inlineStr"/>
+      <c r="P78" s="3" t="inlineStr"/>
+      <c r="Q78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -3396,95 +3571,95 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>occ_g</t>
+          <t>indiv</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Work and exposure</t>
+          <t>Part B: Recent illness</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>ജോലിയും സമ്പർക്കവും</t>
+          <t>ഭാഗം B: അടുത്തിടെയുള്ള അസുഖങ്ങൾ</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr"/>
       <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" s="3" t="inlineStr"/>
-      <c r="H79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>${consent_research}='yes'</t>
+        </is>
+      </c>
       <c r="I79" s="3" t="inlineStr"/>
       <c r="J79" s="3" t="inlineStr"/>
       <c r="K79" s="3" t="inlineStr"/>
       <c r="L79" s="3" t="inlineStr"/>
       <c r="M79" s="3" t="inlineStr"/>
-      <c r="N79" s="3" t="inlineStr">
+      <c r="N79" s="3" t="inlineStr"/>
+      <c r="O79" s="3" t="inlineStr"/>
+      <c r="P79" s="3" t="inlineStr"/>
+      <c r="Q79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>occ_g</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Work and exposure</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>ജോലിയും സമ്പർക്കവും</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr"/>
+      <c r="F80" s="3" t="inlineStr"/>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr"/>
+      <c r="M80" s="3" t="inlineStr"/>
+      <c r="N80" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>select_one occ</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>occupation</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Main occupation</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>പ്രധാന തൊഴിൽ</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>${age} &gt;= 15</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
+      <c r="O80" s="3" t="inlineStr"/>
+      <c r="P80" s="3" t="inlineStr"/>
+      <c r="Q80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one occ</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>wade</t>
+          <t>occupation</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>In the past month, walked through flood or canal water?</t>
+          <t>Main occupation</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>കഴിഞ്ഞ ഒരു മാസത്തിൽ വെള്ളക്കെട്ടിലോ കനാൽ വെള്ളത്തിലോ ഇറങ്ങി നടന്നിട്ടുണ്ടോ?</t>
+          <t>പ്രധാന തൊഴിൽ</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -3494,65 +3669,77 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>${age} &gt;= 15</t>
+        </is>
+      </c>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>select_one yes_no</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>wade</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>In the past month, walked through flood or canal water?</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>കഴിഞ്ഞ ഒരു മാസത്തിൽ വെള്ളക്കെട്ടിലോ കനാൽ വെള്ളത്തിലോ ഇറങ്ങി നടന്നിട്ടുണ്ടോ?</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>horizontal-compact</t>
         </is>
       </c>
-      <c r="O81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>occ_g</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr"/>
-      <c r="D82" s="3" t="inlineStr"/>
-      <c r="E82" s="3" t="inlineStr"/>
-      <c r="F82" s="3" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr"/>
-      <c r="H82" s="3" t="inlineStr"/>
-      <c r="I82" s="3" t="inlineStr"/>
-      <c r="J82" s="3" t="inlineStr"/>
-      <c r="K82" s="3" t="inlineStr"/>
-      <c r="L82" s="3" t="inlineStr"/>
-      <c r="M82" s="3" t="inlineStr"/>
-      <c r="N82" s="3" t="inlineStr"/>
-      <c r="O82" s="3" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>sx_g</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>Past 2 weeks</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>കഴിഞ്ഞ 2 ആഴ്ച</t>
-        </is>
-      </c>
+          <t>occ_g</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" s="3" t="inlineStr"/>
       <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" s="3" t="inlineStr"/>
@@ -3562,81 +3749,69 @@
       <c r="K83" s="3" t="inlineStr"/>
       <c r="L83" s="3" t="inlineStr"/>
       <c r="M83" s="3" t="inlineStr"/>
-      <c r="N83" s="3" t="inlineStr">
+      <c r="N83" s="3" t="inlineStr"/>
+      <c r="O83" s="3" t="inlineStr"/>
+      <c r="P83" s="3" t="inlineStr"/>
+      <c r="Q83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>sx_g</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Past 2 weeks</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>കഴിഞ്ഞ 2 ആഴ്ച</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr"/>
+      <c r="M84" s="3" t="inlineStr"/>
+      <c r="N84" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O83" s="3" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>select_multiple sx</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>sx</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>In the past 2 weeks, any of these?</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>കഴിഞ്ഞ 2 ആഴ്ചയിൽ ഇവയിൽ ഏതെങ്കിലും ഉണ്ടായോ?</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>not(selected(., 'none') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>'None' cannot be combined with other answers.</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>'ഒന്നുമില്ല' മറ്റ് ഉത്തരങ്ങളോടൊപ്പം തിരഞ്ഞെടുക്കാൻ പാടില്ല.</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr"/>
+      <c r="O84" s="3" t="inlineStr"/>
+      <c r="P84" s="3" t="inlineStr"/>
+      <c r="Q84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_multiple sx</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>sx_days</t>
+          <t>sx</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Days unwell</t>
+          <t>In the past 2 weeks, any of these?</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>എത്ര ദിവസം അസുഖമുണ്ടായിരുന്നു?</t>
+          <t>കഴിഞ്ഞ 2 ആഴ്ചയിൽ ഇവയിൽ ഏതെങ്കിലും ഉണ്ടായോ?</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -3646,50 +3821,48 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>count-selected(${sx}) &gt; 0 and not(selected(${sx}, 'none'))</t>
-        </is>
-      </c>
+      <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 14</t>
+          <t>not(selected(., 'none') and count-selected(.) &gt; 1)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Please check this value.</t>
+          <t>'None' cannot be combined with other answers.</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>ഈ മൂല്യം ഒന്നുകൂടി പരിശോധിക്കുക.</t>
+          <t>'ഒന്നുമില്ല' മറ്റ് ഉത്തരങ്ങളോടൊപ്പം തിരഞ്ഞെടുക്കാൻ പാടില്ല.</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>select_one sx_care</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>sx_care</t>
+          <t>sx_days</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Treatment taken</t>
+          <t>Days unwell</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>എടുത്ത ചികിത്സ</t>
+          <t>എത്ര ദിവസം അസുഖമുണ്ടായിരുന്നു?</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -3704,38 +3877,56 @@
           <t>count-selected(${sx}) &gt; 0 and not(selected(${sx}, 'none'))</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 14</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Please check this value.</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>ഈ മൂല്യം ഒന്നുകൂടി പരിശോധിക്കുക.</t>
+        </is>
+      </c>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one sx_care</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>sx_missed</t>
+          <t>sx_care</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Missed work or school?</t>
+          <t>Treatment taken</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>ജോലി / സ്കൂൾ മുടങ്ങിയോ?</t>
+          <t>എടുത്ത ചികിത്സ</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>count-selected(${sx}) &gt; 0 and not(selected(${sx}, 'none'))</t>
@@ -3746,37 +3937,53 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr"/>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>select_one yes_no</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>sx_missed</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Missed work or school?</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>ജോലി / സ്കൂൾ മുടങ്ങിയോ?</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>count-selected(${sx}) &gt; 0 and not(selected(${sx}, 'none'))</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>horizontal-compact</t>
         </is>
       </c>
-      <c r="O87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>sx_g</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr"/>
-      <c r="D88" s="3" t="inlineStr"/>
-      <c r="E88" s="3" t="inlineStr"/>
-      <c r="F88" s="3" t="inlineStr"/>
-      <c r="G88" s="3" t="inlineStr"/>
-      <c r="H88" s="3" t="inlineStr"/>
-      <c r="I88" s="3" t="inlineStr"/>
-      <c r="J88" s="3" t="inlineStr"/>
-      <c r="K88" s="3" t="inlineStr"/>
-      <c r="L88" s="3" t="inlineStr"/>
-      <c r="M88" s="3" t="inlineStr"/>
-      <c r="N88" s="3" t="inlineStr"/>
-      <c r="O88" s="3" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -3786,7 +3993,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>indiv</t>
+          <t>sx_g</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr"/>
@@ -3802,28 +4009,22 @@
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="inlineStr"/>
       <c r="O89" s="3" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr"/>
+      <c r="Q89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>hist</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>Health history</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>ആരോഗ്യ ചരിത്രം</t>
-        </is>
-      </c>
+          <t>indiv</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr"/>
+      <c r="D90" s="3" t="inlineStr"/>
       <c r="E90" s="3" t="inlineStr"/>
       <c r="F90" s="3" t="inlineStr"/>
       <c r="G90" s="3" t="inlineStr"/>
@@ -3833,142 +4034,136 @@
       <c r="K90" s="3" t="inlineStr"/>
       <c r="L90" s="3" t="inlineStr"/>
       <c r="M90" s="3" t="inlineStr"/>
-      <c r="N90" s="3" t="inlineStr">
+      <c r="N90" s="3" t="inlineStr"/>
+      <c r="O90" s="3" t="inlineStr"/>
+      <c r="P90" s="3" t="inlineStr"/>
+      <c r="Q90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>hist</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Health history</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>ആരോഗ്യ ചരിത്രം</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr"/>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr"/>
+      <c r="K91" s="3" t="inlineStr"/>
+      <c r="L91" s="3" t="inlineStr"/>
+      <c r="M91" s="3" t="inlineStr"/>
+      <c r="N91" s="3" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="O90" s="3" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>select_multiple cond</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>conditions</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Known illnesses</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>അറിയാവുന്ന രോഗങ്ങൾ</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>not(selected(., 'none') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>'None' cannot be combined with other answers.</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>'ഒന്നുമില്ല' മറ്റ് ഉത്തരങ്ങളോടൊപ്പം തിരഞ്ഞെടുക്കാൻ പാടില്ല.</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr"/>
-      <c r="O91" s="2" t="inlineStr"/>
+      <c r="O91" s="3" t="inlineStr"/>
+      <c r="P91" s="3" t="inlineStr"/>
+      <c r="Q91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple cond</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>meds</t>
+          <t>conditions</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Medicines taken now</t>
+          <t>Known illnesses</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>ഇപ്പോൾ കഴിക്കുന്ന മരുന്നുകൾ</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Tip: tap the microphone key on the keyboard and speak, in Malayalam or English.</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>കീബോർഡിലെ മൈക്ക് അമർത്തി മലയാളത്തിലോ ഇംഗ്ലീഷിലോ പറഞ്ഞാൽ മതി.</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>not(selected(${conditions}, 'none'))</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
+          <t>അറിയാവുന്ന രോഗങ്ങൾ</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>not(selected(., 'none') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>'None' cannot be combined with other answers.</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>'ഒന്നുമില്ല' മറ്റ് ഉത്തരങ്ങളോടൊപ്പം തിരഞ്ഞെടുക്കാൻ പാടില്ല.</t>
+        </is>
+      </c>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>select_one tob</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>tobacco</t>
+          <t>meds</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Tobacco, paan or areca use</t>
+          <t>Medicines taken now</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>പുകയില / മുറുക്ക് / പാക്ക് ഉപയോഗം</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr"/>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>ഇപ്പോൾ കഴിക്കുന്ന മരുന്നുകൾ</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Tip: tap the microphone key on the keyboard and speak, in Malayalam or English.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>കീബോർഡിലെ മൈക്ക് അമർത്തി മലയാളത്തിലോ ഇംഗ്ലീഷിലോ പറഞ്ഞാൽ മതി.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>${age} &gt;= 12</t>
+          <t>not(selected(${conditions}, 'none'))</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -3976,111 +4171,166 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>select_one tob</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>tobacco</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Tobacco, paan or areca use</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>പുകയില / മുറുക്ക് / പാക്ക് ഉപയോഗം</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>${age} &gt;= 12</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>hist</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr"/>
-      <c r="D94" s="3" t="inlineStr"/>
-      <c r="E94" s="3" t="inlineStr"/>
-      <c r="F94" s="3" t="inlineStr"/>
-      <c r="G94" s="3" t="inlineStr"/>
-      <c r="H94" s="3" t="inlineStr"/>
-      <c r="I94" s="3" t="inlineStr"/>
-      <c r="J94" s="3" t="inlineStr"/>
-      <c r="K94" s="3" t="inlineStr"/>
-      <c r="L94" s="3" t="inlineStr"/>
-      <c r="M94" s="3" t="inlineStr"/>
-      <c r="N94" s="3" t="inlineStr"/>
-      <c r="O94" s="3" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>select_one yes_no</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>contact_ok</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>May we phone you with your results?</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>ഫലങ്ങൾ ഫോണിൽ അറിയിക്കാമോ?</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>string-length(${phone}) &gt; 0</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr">
-        <is>
-          <t>horizontal-compact</t>
-        </is>
-      </c>
-      <c r="O95" s="2" t="inlineStr"/>
+      <c r="C95" s="3" t="inlineStr"/>
+      <c r="D95" s="3" t="inlineStr"/>
+      <c r="E95" s="3" t="inlineStr"/>
+      <c r="F95" s="3" t="inlineStr"/>
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
+      <c r="K95" s="3" t="inlineStr"/>
+      <c r="L95" s="3" t="inlineStr"/>
+      <c r="M95" s="3" t="inlineStr"/>
+      <c r="N95" s="3" t="inlineStr"/>
+      <c r="O95" s="3" t="inlineStr"/>
+      <c r="P95" s="3" t="inlineStr"/>
+      <c r="Q95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>done_note</t>
+          <t>contact_ok</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Done. Write ${person_id} and ${hh_id} on the health card and send the person to measurements.</t>
+          <t>May we phone you with your results?</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>പൂർത്തിയായി. ${person_id}, ${hh_id} ഹെൽത്ത് കാർഡിൽ എഴുതി അളവെടുക്കലിലേക്ക് അയയ്ക്കുക.</t>
+          <t>ഫലങ്ങൾ ഫോണിൽ അറിയിക്കാമോ?</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>string-length(${phone}) &gt; 0</t>
+        </is>
+      </c>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>horizontal-compact</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>done_note</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Done. Write ${person_id} and ${hh_id} on the health card and send the person to measurements.</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>പൂർത്തിയായി. ${person_id}, ${hh_id} ഹെൽത്ത് കാർഡിൽ എഴുതി അളവെടുക്കലിലേക്ക് അയയ്ക്കുക.</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6399,7 +6649,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026102401</t>
+          <t>2026102501</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -6410,6 +6660,59 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>concat(${person_id}, ' · ', ${name})</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>create_if</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>persons</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>concat(${name}, ' (', ${age}, ')')</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>count(instance('persons')/root/item[person_id = ${person_id}]) = 0</t>
         </is>
       </c>
     </row>
